--- a/catalogo_productos.xlsx
+++ b/catalogo_productos.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$K$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Productos'!$A$1:$L$103</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -527,6 +528,11 @@
           <t>PrecioAnterior</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20.1" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -797,7 +803,11 @@
       <c r="D8" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/10109.jpg</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -834,7 +844,11 @@
       <c r="D9" s="4" t="n">
         <v>14000</v>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2907.jpg</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -871,7 +885,11 @@
       <c r="D10" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="E10" s="3" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2910.jpg</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -908,7 +926,11 @@
       <c r="D11" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="E11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2913.jpg</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -945,7 +967,11 @@
       <c r="D12" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="E12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3510.jpg</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -982,7 +1008,11 @@
       <c r="D13" s="4" t="n">
         <v>9500</v>
       </c>
-      <c r="E13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2916.jpg</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -1019,7 +1049,11 @@
       <c r="D14" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="E14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4815.jpg</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>3 rollos (50 paños)</t>
@@ -1056,7 +1090,11 @@
       <c r="D15" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="E15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2800.jpg</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
           <t>1 rollo (200 paños)</t>
@@ -1093,7 +1131,11 @@
       <c r="D16" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4851.jpg</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>4 rollos x 30m</t>
@@ -1115,25 +1157,29 @@
     </row>
     <row r="17" ht="20.1" customHeight="1">
       <c r="A17" s="2" t="n">
-        <v>3138</v>
+        <v>3579</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Higienol Doble Hoja Plus x4</t>
+          <t>Campanita Plus Papel Higiénico x4</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Papel higiénico doble hoja con máxima textura, suavidad y resistencia.</t>
+          <t>Papel higiénico Campanita Plus. Pack de 4 rollos de 30 metros.</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E17" s="3" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3579.jpg</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>4 rollos x 30m</t>
+          <t>4 rollos x 30 m</t>
         </is>
       </c>
       <c r="G17" s="3" t="n"/>
@@ -1144,7 +1190,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/papel-higienico-higienol-d-hoja-30m-x4-plus-3138</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/papel-higienico-campanita-plus-4x30m-3579</t>
         </is>
       </c>
       <c r="J17" s="2" t="n"/>
@@ -1152,25 +1198,29 @@
     </row>
     <row r="18" ht="20.1" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>2164</v>
+        <v>4723</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Campanita Toalla Intercalada Blanca x2500</t>
+          <t>Campanita Ultra Doble Hoja x4</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Toallas de papel intercaladas premium blancas (20x24cm) de hoja simple para dispenser institucional.</t>
+          <t>Papel higiénico doble hoja. Pack de 4 rollos de 30 metros.</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E18" s="3" t="n"/>
+        <v>3000</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4723.jpg</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Caja x 2500 toallas</t>
+          <t>4 rollos x 30 m</t>
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
@@ -1181,7 +1231,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/toalla-blanca-premium-x2500-20x24cm-intercaladas-2164</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/papel-higienico-campanita-d-h-30mx4-ultra-4723</t>
         </is>
       </c>
       <c r="J18" s="2" t="n"/>
@@ -1189,25 +1239,29 @@
     </row>
     <row r="19" ht="20.1" customHeight="1">
       <c r="A19" s="2" t="n">
-        <v>100</v>
+        <v>4013</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Papel Higiénico Jumbo 8x300m Palacio</t>
+          <t>Campanita Servilletas 32x30cm x800</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bobinas institucionales de papel higiénico con cono chico para dispensers de alto tránsito.</t>
+          <t>Servilletas de papel Campanita. Medidas 32 x 30 cm.</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E19" s="3" t="n"/>
+        <v>18000</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4013.jpg</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>8 rollos x 300m</t>
+          <t>Pack x 800 un.</t>
         </is>
       </c>
       <c r="G19" s="3" t="n"/>
@@ -1218,7 +1272,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/papel-higienico-8x300m-cono-chico-palacio-100</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/servilletas-32x30x1000-campanita-4013</t>
         </is>
       </c>
       <c r="J19" s="2" t="n"/>
@@ -1241,7 +1295,11 @@
       <c r="D20" s="4" t="n">
         <v>25999</v>
       </c>
-      <c r="E20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/6221.jpg</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Caja x 2500 toallas</t>
@@ -1263,25 +1321,29 @@
     </row>
     <row r="21" ht="20.1" customHeight="1">
       <c r="A21" s="2" t="n">
-        <v>6211</v>
+        <v>2164</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Toalla en Rollo Blanca 2x300m Palacio</t>
+          <t>Campanita Toalla Intercalada Blanca x2500</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Bobinas de papel toalla blanco de 20cm para dispenser de toalla a palanca o corte automático.</t>
+          <t>Toallas de papel intercaladas premium blancas (20x24cm) de hoja simple para dispenser institucional.</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E21" s="3" t="n"/>
+        <v>32000</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2164.jpg</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2 rollos x 300m</t>
+          <t>Caja x 2500 toallas</t>
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
@@ -1290,31 +1352,39 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.elpalaciodelalimpieza.com.ar/toalla-blanca-premium-x2500-20x24cm-intercaladas-2164</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="3" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1">
       <c r="A22" s="2" t="n">
-        <v>100280</v>
+        <v>3676</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Elite / Carilina Pañuelos Descartables</t>
+          <t>EccoSoft Bobina Doble Hoja 2x400m</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Pañuelos de bolsillo descartables triples, suaves y resistentes al uso.</t>
+          <t>Bobinas de papel blanco doble hoja de 24 cm de ancho.</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1900</v>
-      </c>
-      <c r="E22" s="3" t="n"/>
+        <v>38000</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3676.jpg</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>6 paq. x 10 un.</t>
+          <t>2 bobinas x 400 m</t>
         </is>
       </c>
       <c r="G22" s="3" t="n"/>
@@ -1325,7 +1395,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/elite-pa-uelos-x6-paquetes-100280</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/bobina-24cm-x400m-x2-blanca-eccosoft-doble-hoja-3676</t>
         </is>
       </c>
       <c r="J22" s="2" t="n"/>
@@ -1333,25 +1403,29 @@
     </row>
     <row r="23" ht="20.1" customHeight="1">
       <c r="A23" s="2" t="n">
-        <v>2226</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Elite Pañuelos Descartables Caja x75</t>
+          <t>Papel Higiénico Jumbo 8x300m Palacio</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Caja dispensadora decorativa de pañuelos faciales descartables extra suaves.</t>
+          <t>Bobinas institucionales de papel higiénico con cono chico para dispensers de alto tránsito.</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1900</v>
-      </c>
-      <c r="E23" s="3" t="n"/>
+        <v>20000</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/100.jpg</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Caja x 75 un.</t>
+          <t>8 rollos x 300m</t>
         </is>
       </c>
       <c r="G23" s="3" t="n"/>
@@ -1362,7 +1436,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/elite-pa-uelos-x75-caja-2226</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/papel-higienico-8x300m-cono-chico-palacio-100</t>
         </is>
       </c>
       <c r="J23" s="2" t="n"/>
@@ -1370,25 +1444,29 @@
     </row>
     <row r="24" ht="20.1" customHeight="1">
       <c r="A24" s="2" t="n">
-        <v>639</v>
+        <v>10114</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Trapo de Piso Gris XG Media Naranja</t>
+          <t>Make Rollo de Aluminio 5m</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Trapo de piso extra grande tejido en hilado de algodón puro. Gran poder de absorción y durabilidad.</t>
+          <t>Rollo de papel de aluminio para uso en cocina.</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="E24" s="3" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/10114.jpg</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>60 x 80 cm</t>
+          <t>5 metros</t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
@@ -1399,7 +1477,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/media-naranja-trapo-de-piso-gris-xg-60x80cm-639</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/rollo-aluminio-make-5m-10114</t>
         </is>
       </c>
       <c r="J24" s="2" t="n"/>
@@ -1407,25 +1485,29 @@
     </row>
     <row r="25" ht="20.1" customHeight="1">
       <c r="A25" s="2" t="n">
-        <v>674</v>
+        <v>4351</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Ballerina Paños Multiuso x3</t>
+          <t>Make Film Adherente 30m</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Paños sintéticos absorbentes multiuso para lavado, limpieza y secado de todas las superficies.</t>
+          <t>Rollo de film adherente para cubrir y envolver alimentos.</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5900</v>
-      </c>
-      <c r="E25" s="3" t="n"/>
+        <v>2100</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4351.jpg</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Pack x 3 paños</t>
+          <t>30 metros</t>
         </is>
       </c>
       <c r="G25" s="3" t="n"/>
@@ -1436,7 +1518,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/ballerina-pa-o-multiuso-x3-674</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/rollo-film-adherente-30m-make-4351</t>
         </is>
       </c>
       <c r="J25" s="2" t="n"/>
@@ -1459,7 +1541,11 @@
       <c r="D26" s="4" t="n">
         <v>2600</v>
       </c>
-      <c r="E26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2444.jpg</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>2 litros</t>
@@ -1496,7 +1582,11 @@
       <c r="D27" s="4" t="n">
         <v>1250</v>
       </c>
-      <c r="E27" s="3" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/48.jpg</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t>1 litro</t>
@@ -1533,7 +1623,11 @@
       <c r="D28" s="4" t="n">
         <v>14500</v>
       </c>
-      <c r="E28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4590.jpg</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
           <t>1 litro</t>
@@ -1570,7 +1664,11 @@
       <c r="D29" s="4" t="n">
         <v>3500</v>
       </c>
-      <c r="E29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4429.jpg</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
           <t>700 ml</t>
@@ -1592,36 +1690,32 @@
     </row>
     <row r="30" ht="20.1" customHeight="1">
       <c r="A30" s="2" t="n">
-        <v>158</v>
+        <v>7605</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Blem Lustramuebles Aero</t>
+          <t>Bialcohol Alcohol Fino 70% 5L</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Aerosol lustramuebles que limpia, protege y realza el brillo natural de los muebles.</t>
+          <t>Alcohol fino al 70% Bialcohol en bidón de 5 litros.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6200</v>
+        <v>22000</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>imagenes/158.jpg</t>
+          <t>imagenes/7605.jpg</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>360 ml</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Original, Naranja, Lavanda</t>
-        </is>
-      </c>
+          <t>5 litros</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1629,7 +1723,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/blem-aero-360-marron-158</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/alcohol-fino-70-5l-bialcohol-7605</t>
         </is>
       </c>
       <c r="J30" s="2" t="n"/>
@@ -1637,36 +1731,32 @@
     </row>
     <row r="31" ht="20.1" customHeight="1">
       <c r="A31" s="2" t="n">
-        <v>424</v>
+        <v>7601</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Lysoform Aero</t>
+          <t>Bialcohol Alcohol Fino 96° 5L</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Aerosol desinfectante que ayuda a eliminar gérmenes y bacterias, dejando los ambientes más higienizados.</t>
+          <t>Alcohol fino de 96° Bialcohol en bidón de 5 litros.</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4800</v>
+        <v>25000</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>imagenes/424.jpg</t>
+          <t>imagenes/7601.jpg</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>360 ml</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Original, Cítrico, Bebé, Aire de montaña, Lavanda</t>
-        </is>
-      </c>
+          <t>5 litros</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1674,7 +1764,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/lysoform-aero-360-380-original-424</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/bialcohol-fino-96-5l-7601</t>
         </is>
       </c>
       <c r="J31" s="2" t="n"/>
@@ -1697,7 +1787,11 @@
       <c r="D32" s="4" t="n">
         <v>8500</v>
       </c>
-      <c r="E32" s="3" t="n"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/602.jpg</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>360 cc</t>
@@ -1734,7 +1828,11 @@
       <c r="D33" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="E33" s="3" t="n"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/611.jpg</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
           <t>170 cc</t>
@@ -1756,28 +1854,36 @@
     </row>
     <row r="34" ht="20.1" customHeight="1">
       <c r="A34" s="2" t="n">
-        <v>2485</v>
+        <v>424</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Make Aromatizante de Ambiente Cítrico</t>
+          <t>Lysoform Aero</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Aromatizante ambiental en aerosol con fragancia cítrica estimulante y prolongada.</t>
+          <t>Aerosol desinfectante que ayuda a eliminar gérmenes y bacterias, dejando los ambientes más higienizados.</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
         <v>4800</v>
       </c>
-      <c r="E34" s="3" t="n"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/424.jpg</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Aerosol</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n"/>
+          <t>360 ml</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Original, Cítrico, Bebé, Aire de montaña, Lavanda</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1785,7 +1891,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/make-aromatizante-aero-citrico-2485</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/lysoform-aero-360-380-original-424</t>
         </is>
       </c>
       <c r="J34" s="2" t="n"/>
@@ -1793,28 +1899,36 @@
     </row>
     <row r="35" ht="20.1" customHeight="1">
       <c r="A35" s="2" t="n">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Mr Músculo Limpia Horno Aerosol</t>
+          <t>Blem Lustramuebles Aero</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Espuma activa para limpieza de hornos, parrillas y asaderas que ablanda la grasa quemada sin raspar.</t>
+          <t>Aerosol lustramuebles que limpia, protege y realza el brillo natural de los muebles.</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E35" s="3" t="n"/>
+        <v>6200</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/158.jpg</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>360 cc</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n"/>
+          <t>360 ml</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Original, Naranja, Lavanda</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
@@ -1822,7 +1936,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/mister-musculo-horno-aero-400cc-103</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/blem-aero-360-marron-158</t>
         </is>
       </c>
       <c r="J35" s="2" t="n"/>
@@ -1830,25 +1944,29 @@
     </row>
     <row r="36" ht="20.1" customHeight="1">
       <c r="A36" s="2" t="n">
-        <v>4100</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Magistral Detergente Limón 750ml</t>
+          <t>Mr Músculo Limpia Horno Aerosol</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Detergente lavavajillas ultra concentrado con alto poder desengrasante y aroma a limón.</t>
+          <t>Espuma activa para limpieza de hornos, parrillas y asaderas que ablanda la grasa quemada sin raspar.</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E36" s="3" t="n"/>
+        <v>9500</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/103.jpg</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>360 cc</t>
         </is>
       </c>
       <c r="G36" s="3" t="n"/>
@@ -1859,7 +1977,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/magistral-750-limon-4100</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/mister-musculo-horno-aero-400cc-103</t>
         </is>
       </c>
       <c r="J36" s="2" t="n"/>
@@ -1867,25 +1985,29 @@
     </row>
     <row r="37" ht="20.1" customHeight="1">
       <c r="A37" s="2" t="n">
-        <v>37</v>
+        <v>3314</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Cif Active Gel Detergente Limón 750ml</t>
+          <t>Make Aromatizante Rosas</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Detergente con micro-espuma activa que disuelve la grasa más rebelde en vajilla y ollas.</t>
+          <t>Aromatizante de ambiente en aerosol con fragancia a rosas.</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E37" s="3" t="n"/>
+        <v>4800</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3314.jpg</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>750 ml</t>
+          <t>Aerosol</t>
         </is>
       </c>
       <c r="G37" s="3" t="n"/>
@@ -1896,7 +2018,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cif-detergente-750-limon-37</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/make-aromatizante-aero-rosas-3314</t>
         </is>
       </c>
       <c r="J37" s="2" t="n"/>
@@ -1904,25 +2026,29 @@
     </row>
     <row r="38" ht="20.1" customHeight="1">
       <c r="A38" s="2" t="n">
-        <v>261</v>
+        <v>3329</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Cif Antigrasa Doypack 450ml</t>
+          <t>Cif Detergente Neutro Institucional 5L</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Limpiador antigrasa desengrasante instantáneo para mesadas, anafes y campanas de cocina.</t>
+          <t>Detergente neutro concentrado de uso profesional para gastronomía e industrias.</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E38" s="3" t="n"/>
+        <v>27000</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3329.jpg</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>450 ml (doypack)</t>
+          <t>5 litros</t>
         </is>
       </c>
       <c r="G38" s="3" t="n"/>
@@ -1933,7 +2059,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cif-antigrasa-450-d-pack-261</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cif-detergente-5l-neutro-3329</t>
         </is>
       </c>
       <c r="J38" s="2" t="n"/>
@@ -1941,22 +2067,26 @@
     </row>
     <row r="39" ht="20.1" customHeight="1">
       <c r="A39" s="2" t="n">
-        <v>3329</v>
+        <v>5176</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Cif Detergente Neutro Institucional 5L</t>
+          <t>Cif Vidrios Institucional 5L</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Detergente neutro concentrado de uso profesional para gastronomía e industrias.</t>
+          <t>Limpiador de vidrios y superficies brillantes profesional, sin aureolas ni residuos.</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>27000</v>
-      </c>
-      <c r="E39" s="3" t="n"/>
+        <v>20000</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5176.jpg</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -1970,7 +2100,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cif-detergente-5l-neutro-3329</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cif-vidrios-5l-5176</t>
         </is>
       </c>
       <c r="J39" s="2" t="n"/>
@@ -1978,22 +2108,26 @@
     </row>
     <row r="40" ht="20.1" customHeight="1">
       <c r="A40" s="2" t="n">
-        <v>5176</v>
+        <v>1130</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cif Vidrios Institucional 5L</t>
+          <t>8M Cera Líquida Express Incolora 5L</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Limpiador de vidrios y superficies brillantes profesional, sin aureolas ni residuos.</t>
+          <t>Cera autobrillante incolora de secado rápido apta para pisos cerámicos, mosaicos y cemento alisado.</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E40" s="3" t="n"/>
+        <v>35000</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1130.jpg</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>5 litros</t>
@@ -2007,7 +2141,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cif-vidrios-5l-5176</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/8m-5l-express-incoloro-1130</t>
         </is>
       </c>
       <c r="J40" s="2" t="n"/>
@@ -2030,7 +2164,11 @@
       <c r="D41" s="4" t="n">
         <v>16500</v>
       </c>
-      <c r="E41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/100147.jpg</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>2 litros (3 kg)</t>
@@ -2052,25 +2190,29 @@
     </row>
     <row r="42" ht="20.1" customHeight="1">
       <c r="A42" s="2" t="n">
-        <v>1130</v>
+        <v>5010</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>8M Cera Líquida Express Incolora 5L</t>
+          <t>Media Naranja Paños Multiuso x3</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Cera autobrillante incolora de secado rápido apta para pisos cerámicos, mosaicos y cemento alisado.</t>
+          <t>Paños multiuso amarillos de 38 x 40 cm.</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E42" s="3" t="n"/>
+        <v>2800</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5010.jpg</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>5 litros</t>
+          <t>Pack x 3 un.</t>
         </is>
       </c>
       <c r="G42" s="3" t="n"/>
@@ -2081,7 +2223,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/8m-5l-express-incoloro-1130</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/media-naranja-pa-o-mult-x3-38x40-5010</t>
         </is>
       </c>
       <c r="J42" s="2" t="n"/>
@@ -2089,25 +2231,29 @@
     </row>
     <row r="43" ht="20.1" customHeight="1">
       <c r="A43" s="2" t="n">
-        <v>470</v>
+        <v>10090</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Drastik Desengrasante Concentrado 500cc</t>
+          <t>Franela Clásica Media Naranja</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Desengrasante de alta potencia para suciedades pesadas, motores, maquinarias y filtros.</t>
+          <t>Franela de algodón suave para lustrar, limpiar muebles, vidrios y pulir superficies sin rayar.</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E43" s="3" t="n"/>
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/10090.jpg</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>500 cc</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="G43" s="3" t="n"/>
@@ -2118,7 +2264,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/drastik-500cc-470</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/franela-clasica-media-naranja-10090</t>
         </is>
       </c>
       <c r="J43" s="2" t="n"/>
@@ -2126,25 +2272,29 @@
     </row>
     <row r="44" ht="20.1" customHeight="1">
       <c r="A44" s="2" t="n">
-        <v>3128</v>
+        <v>538</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Skip Jabón Líquido Doypack 3L</t>
+          <t>Mortimer Esponja Cuadriculada</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido para lavarropas automático con tecnología Bio-Enzimas para remoción de manchas difíciles.</t>
+          <t>Esponja multiuso con diseño cuadriculado de espuma sintética y fibra abrasiva integrada.</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>12500</v>
-      </c>
-      <c r="E44" s="3" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/538.jpg</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>3 litros (30 lavados)</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
@@ -2155,7 +2305,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/skip-liquido-3l-d-p-30-lavados-3128</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/mortimer-cuadriculada-clasica-538</t>
         </is>
       </c>
       <c r="J44" s="2" t="n"/>
@@ -2163,25 +2313,29 @@
     </row>
     <row r="45" ht="20.1" customHeight="1">
       <c r="A45" s="2" t="n">
-        <v>26</v>
+        <v>1561</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Ala Jabón Líquido Clásico Doypack 3L</t>
+          <t>Mortimer Esponja Doble Cara</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido para lavado de ropa de uso cotidiano con alto poder de limpieza y cuidado de telas.</t>
+          <t>Esponja anatómica salvaúñas con fibra abrasiva para limpieza profunda y esponja para enjabonar.</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E45" s="3" t="n"/>
+        <v>2600</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1561.jpg</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>3 litros</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="G45" s="3" t="n"/>
@@ -2192,7 +2346,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/ala-jabon-liquido-3l-clasico-d-pack-26</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/mortimer-esp-doble-cara-1561</t>
         </is>
       </c>
       <c r="J45" s="2" t="n"/>
@@ -2200,25 +2354,29 @@
     </row>
     <row r="46" ht="20.1" customHeight="1">
       <c r="A46" s="2" t="n">
-        <v>3069</v>
+        <v>5487</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Granby Jabón Líquido Rosas Doypack 3L</t>
+          <t>Make Esponja de Acero Inoxidable 50g</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido para ropa con fragancia floral a rosas, económico y rendidor en cada lavado.</t>
+          <t>Espiral de acero inoxidable para fregar ollas, parrillas y suciedad pegada muy rebelde.</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E46" s="3" t="n"/>
+        <v>1500</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5487.jpg</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>3 litros</t>
+          <t>50 gramos</t>
         </is>
       </c>
       <c r="G46" s="3" t="n"/>
@@ -2229,7 +2387,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/granby-liq-ropa-3l-d-p-rosas-3069</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/make-esponja-inoxidable-50g-5487</t>
         </is>
       </c>
       <c r="J46" s="2" t="n"/>
@@ -2237,25 +2395,29 @@
     </row>
     <row r="47" ht="20.1" customHeight="1">
       <c r="A47" s="2" t="n">
-        <v>1660</v>
+        <v>524</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Ariel Platinum Jabón Líquido Pouch 3L</t>
+          <t>Virulana Rollitos Lana de Acero x10</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido concentrado con tecnología de brillo y máxima blancura sin desgastar las prendas.</t>
+          <t>Rollitos de viruta fina de acero para pulido de metales, aluminio y ollas tradicionales.</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E47" s="3" t="n"/>
+        <v>2300</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/524.jpg</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>3 litros</t>
+          <t>Pack x 10 un. (70g)</t>
         </is>
       </c>
       <c r="G47" s="3" t="n"/>
@@ -2266,7 +2428,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/ariel-liq-2-7l-pouch-maxima-limpieza-1660</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/virulana-rollitos-x10-70g-524</t>
         </is>
       </c>
       <c r="J47" s="2" t="n"/>
@@ -2274,25 +2436,29 @@
     </row>
     <row r="48" ht="20.1" customHeight="1">
       <c r="A48" s="2" t="n">
-        <v>2111</v>
+        <v>55</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Vivere Suavizante Clásico Doypack 3L</t>
+          <t>Make Guantes de Látex Soft Mediano</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Suavizante para ropa que deja las fibras suaves y esponjosas con fragancia intensa.</t>
+          <t>Guantes de látex satinado para protección de las manos en tareas domésticas cotidianas.</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E48" s="3" t="n"/>
+        <v>1650</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/55.jpg</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>3 litros</t>
+          <t>Par (Talle M)</t>
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
@@ -2303,7 +2469,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/vivere-3l-clasico-d-pack-2111</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/make-guante-soft-mediano-55</t>
         </is>
       </c>
       <c r="J48" s="2" t="n"/>
@@ -2311,25 +2477,29 @@
     </row>
     <row r="49" ht="20.1" customHeight="1">
       <c r="A49" s="2" t="n">
-        <v>2110</v>
+        <v>733</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Comfort Suavizante Classic Doypack 3L</t>
+          <t>MAPA Guantes Plissé Talle 7½-8</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Suavizante textil concentrado que protege contra la formación de pelotitas y facilita el planchado.</t>
+          <t>Guantes profesionales de látex natural reforzado con puño plisado de máxima durabilidad.</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>13500</v>
-      </c>
-      <c r="E49" s="3" t="n"/>
+        <v>3900</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/733.jpg</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>3 litros</t>
+          <t>Par (Talle M)</t>
         </is>
       </c>
       <c r="G49" s="3" t="n"/>
@@ -2340,7 +2510,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/comfort-3l-classic-d-pack-2110</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/mapa-guantes-plisse-7-8-med-733</t>
         </is>
       </c>
       <c r="J49" s="2" t="n"/>
@@ -2348,25 +2518,29 @@
     </row>
     <row r="50" ht="20.1" customHeight="1">
       <c r="A50" s="2" t="n">
-        <v>1353</v>
+        <v>1434</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Downy Suavizante Brisa Suave 1L</t>
+          <t>Romyl Pala Aeropuerto con Escoba</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Suavizante premium con microcápsulas de fragancia que se activan con el movimiento.</t>
+          <t>Pala recolectora tipo aeropuerto con escoba incluida.</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>13900</v>
-      </c>
-      <c r="E50" s="3" t="n"/>
+        <v>12500</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1434.jpg</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>1 litro</t>
+          <t>Pala + escoba</t>
         </is>
       </c>
       <c r="G50" s="3" t="n"/>
@@ -2377,7 +2551,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/downy-suavizante-1l-brisa-verano-1353</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/pala-aeropuerto-romyl-c-escoba-1434</t>
         </is>
       </c>
       <c r="J50" s="2" t="n"/>
@@ -2385,25 +2559,29 @@
     </row>
     <row r="51" ht="20.1" customHeight="1">
       <c r="A51" s="2" t="n">
-        <v>1007</v>
+        <v>1758</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Dove Jabón de Tocador Original 90g</t>
+          <t>Balde Plástico 12 Litros Romyl</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Barra de limpieza con 1/4 de crema humectante que respeta la barrera natural de la piel.</t>
+          <t>Balde de polipropileno reforzado con asa metálica y escala de litros para limpieza.</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E51" s="3" t="n"/>
+        <v>5500</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1758.jpg</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>90 gramos</t>
+          <t>12 litros</t>
         </is>
       </c>
       <c r="G51" s="3" t="n"/>
@@ -2414,7 +2592,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dove-jabon-90g-clasico-pc-1007</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/balde-12l-romyl-task-1758</t>
         </is>
       </c>
       <c r="J51" s="2" t="n"/>
@@ -2422,25 +2600,29 @@
     </row>
     <row r="52" ht="20.1" customHeight="1">
       <c r="A52" s="2" t="n">
-        <v>10244</v>
+        <v>10098</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Dove Jabón Líquido Manos Doypack 220ml</t>
+          <t>Clean-tex Trapo de Piso Blanco</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido para higiene de manos con nutrición profunda y textura cremosa.</t>
+          <t>Trapo de piso blanco Consorcio de 60 x 70 cm.</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>3400</v>
-      </c>
-      <c r="E52" s="3" t="n"/>
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/10098.jpg</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>220 ml (repuesto)</t>
+          <t>60 x 70 cm</t>
         </is>
       </c>
       <c r="G52" s="3" t="n"/>
@@ -2451,7 +2633,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dove-jabon-liq-220-rep-nutricion-profunda-10244</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/clean-tex-trapo-de-piso-blanco-60x70-consorcio-10098</t>
         </is>
       </c>
       <c r="J52" s="2" t="n"/>
@@ -2459,25 +2641,29 @@
     </row>
     <row r="53" ht="20.1" customHeight="1">
       <c r="A53" s="2" t="n">
-        <v>1587</v>
+        <v>3747</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Rexona Jabón Líquido Antibacterial 250ml</t>
+          <t>Romyl Balde Oval con Escurridor</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Jabón líquido antibacterial para manos que elimina el 99.9% de gérmenes con fragancia fresca.</t>
+          <t>Balde oval de 14 litros con escurridor.</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E53" s="3" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3747.jpg</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>250 ml</t>
+          <t>14 litros</t>
         </is>
       </c>
       <c r="G53" s="3" t="n"/>
@@ -2488,7 +2674,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/rexona-jabon-liq-antib-250-full-aloe-1587</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/balde-oval-14l-c-escurr-romyl-samantha-3747</t>
         </is>
       </c>
       <c r="J53" s="2" t="n"/>
@@ -2496,25 +2682,29 @@
     </row>
     <row r="54" ht="20.1" customHeight="1">
       <c r="A54" s="2" t="n">
-        <v>112</v>
+        <v>3775</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Segovia Pastillas para Mingitorio 200g</t>
+          <t>Palacio Trapo de Piso Premium</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Pastillas desodorizantes que neutralizan olores y mantienen higienizados los mingitorios.</t>
+          <t>Trapo de piso Premium de 60 x 56 cm.</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E54" s="3" t="n"/>
+        <v>4500</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3775.jpg</t>
+        </is>
+      </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>200 gramos</t>
+          <t>60 x 56 cm</t>
         </is>
       </c>
       <c r="G54" s="3" t="n"/>
@@ -2525,7 +2715,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/bolitas-mingitorio-200g-112</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/trapo-piso-premium-60x56cm-palacio-3775</t>
         </is>
       </c>
       <c r="J54" s="2" t="n"/>
@@ -2533,25 +2723,29 @@
     </row>
     <row r="55" ht="20.1" customHeight="1">
       <c r="A55" s="2" t="n">
-        <v>2845</v>
+        <v>3750</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Duke Jabón Hotelero Envuelto 20g x240</t>
+          <t>Palacio Rejilla Premium</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Jaboncitos individuales envueltos de tocador ideales para hoteles, posadas y sanatorios.</t>
+          <t>Paño rejilla Premium para limpieza cotidiana.</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E55" s="3" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3750.jpg</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Caja x 240 un. (20g)</t>
+          <t>40 x 30 cm</t>
         </is>
       </c>
       <c r="G55" s="3" t="n"/>
@@ -2562,7 +2756,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/duke-hotel-20g-x240-envuelto-2845</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/rejilla-premium-40x30cm-palacio-3750</t>
         </is>
       </c>
       <c r="J55" s="2" t="n"/>
@@ -2570,25 +2764,29 @@
     </row>
     <row r="56" ht="20.1" customHeight="1">
       <c r="A56" s="2" t="n">
-        <v>5400</v>
+        <v>3069</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Suave Shampoo Nutrición Coco 5L</t>
+          <t>Granby Jabón Líquido Rosas Doypack 3L</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Shampoo institucional nutritivo con extracto de coco y proteínas para uso diario familiar o vestuarios.</t>
+          <t>Jabón líquido para ropa con fragancia floral a rosas, económico y rendidor en cada lavado.</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>23000</v>
-      </c>
-      <c r="E56" s="3" t="n"/>
+        <v>9500</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3069.jpg</t>
+        </is>
+      </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>5 litros</t>
+          <t>3 litros</t>
         </is>
       </c>
       <c r="G56" s="3" t="n"/>
@@ -2599,7 +2797,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/p-allen-sh-930-rosa-mosqueta</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/granby-liq-ropa-3l-d-p-rosas-3069</t>
         </is>
       </c>
       <c r="J56" s="2" t="n"/>
@@ -2607,25 +2805,29 @@
     </row>
     <row r="57" ht="20.1" customHeight="1">
       <c r="A57" s="2" t="n">
-        <v>3807</v>
+        <v>1660</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Suave Acondicionador Nutrición Coco 5L</t>
+          <t>Ariel Platinum Jabón Líquido Pouch 3L</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Acondicionador desenredante y humectante con aroma a coco en bidón institucional.</t>
+          <t>Jabón líquido concentrado con tecnología de brillo y máxima blancura sin desgastar las prendas.</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>23000</v>
-      </c>
-      <c r="E57" s="3" t="n"/>
+        <v>12000</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1660.jpg</t>
+        </is>
+      </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>5 litros</t>
+          <t>3 litros</t>
         </is>
       </c>
       <c r="G57" s="3" t="n"/>
@@ -2636,7 +2838,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/p-allen-sh-960-guarana</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/ariel-liq-2-7l-pouch-maxima-limpieza-1660</t>
         </is>
       </c>
       <c r="J57" s="2" t="n"/>
@@ -2644,25 +2846,29 @@
     </row>
     <row r="58" ht="20.1" customHeight="1">
       <c r="A58" s="2" t="n">
-        <v>4399</v>
+        <v>2111</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Sedal Shampoo Crema Balance Doypack 300ml</t>
+          <t>Vivere Suavizante Clásico Doypack 3L</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Shampoo para hidratación cotidiana y equilibrio del cabello con complejo vitamínico.</t>
+          <t>Suavizante para ropa que deja las fibras suaves y esponjosas con fragancia intensa.</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E58" s="3" t="n"/>
+        <v>12000</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2111.jpg</t>
+        </is>
+      </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>300 ml (doypack)</t>
+          <t>3 litros</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -2673,7 +2879,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/sedal-shampoo-300-d-p-crema-balance-4399</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/vivere-3l-clasico-d-pack-2111</t>
         </is>
       </c>
       <c r="J58" s="2" t="n"/>
@@ -2681,25 +2887,29 @@
     </row>
     <row r="59" ht="20.1" customHeight="1">
       <c r="A59" s="2" t="n">
-        <v>1000013</v>
+        <v>2110</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Sedal Acondicionador Crema Balance 300ml</t>
+          <t>Comfort Suavizante Classic Doypack 3L</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Acondicionador desenredante suave para un pelo sedoso y brillante todos los días.</t>
+          <t>Suavizante textil concentrado que protege contra la formación de pelotitas y facilita el planchado.</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E59" s="3" t="n"/>
+        <v>13500</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2110.jpg</t>
+        </is>
+      </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>300 ml (doypack)</t>
+          <t>3 litros</t>
         </is>
       </c>
       <c r="G59" s="3" t="n"/>
@@ -2710,7 +2920,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/sedal-acondicionador-300-d-p-crema-balance-1000013</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/comfort-3l-classic-d-pack-2110</t>
         </is>
       </c>
       <c r="J59" s="2" t="n"/>
@@ -2718,25 +2928,29 @@
     </row>
     <row r="60" ht="20.1" customHeight="1">
       <c r="A60" s="2" t="n">
-        <v>6646</v>
+        <v>112</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Dove Shampoo Reconstrucción Doypack 180ml</t>
+          <t>Segovia Pastillas para Mingitorio 200g</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Shampoo con activos reparadores para cabellos quebradizos o expuestos a daño térmico.</t>
+          <t>Pastillas desodorizantes que neutralizan olores y mantienen higienizados los mingitorios.</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E60" s="3" t="n"/>
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/112.jpg</t>
+        </is>
+      </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>180 ml (doypack)</t>
+          <t>200 gramos</t>
         </is>
       </c>
       <c r="G60" s="3" t="n"/>
@@ -2747,7 +2961,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dove-shampoo-180-d-p-cabello-da-ado-6646</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/bolitas-mingitorio-200g-112</t>
         </is>
       </c>
       <c r="J60" s="2" t="n"/>
@@ -2755,25 +2969,29 @@
     </row>
     <row r="61" ht="20.1" customHeight="1">
       <c r="A61" s="2" t="n">
-        <v>6645</v>
+        <v>2845</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Dove Acondicionador Reconstrucción 180ml</t>
+          <t>Duke Jabón Hotelero Envuelto 20g x240</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Acondicionador de acción profunda para restaurar la fibra capilar y evitar puntas abiertas.</t>
+          <t>Jaboncitos individuales envueltos de tocador ideales para hoteles, posadas y sanatorios.</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E61" s="3" t="n"/>
+        <v>65000</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2845.jpg</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>180 ml (doypack)</t>
+          <t>Caja x 240 un. (20g)</t>
         </is>
       </c>
       <c r="G61" s="3" t="n"/>
@@ -2784,7 +3002,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dove-acondicionador-180-d-p-cabello-da-ado-6645</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/duke-hotel-20g-x240-envuelto-2845</t>
         </is>
       </c>
       <c r="J61" s="2" t="n"/>
@@ -2792,25 +3010,29 @@
     </row>
     <row r="62" ht="20.1" customHeight="1">
       <c r="A62" s="2" t="n">
-        <v>952</v>
+        <v>5400</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Pantene Shampoo Rizos Definidos 400ml</t>
+          <t>Suave Shampoo Nutrición Coco 5L</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Shampoo con infusión Pro-V para hidratación y memoria de ondas y rulos sin frizz.</t>
+          <t>Shampoo institucional nutritivo con extracto de coco y proteínas para uso diario familiar o vestuarios.</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E62" s="3" t="n"/>
+        <v>23000</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5400.jpg</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>400 ml</t>
+          <t>5 litros</t>
         </is>
       </c>
       <c r="G62" s="3" t="n"/>
@@ -2819,31 +3041,39 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I62" s="3" t="n"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.elpalaciodelalimpieza.com.ar</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="3" t="n"/>
     </row>
     <row r="63" ht="20.1" customHeight="1">
       <c r="A63" s="2" t="n">
-        <v>100130</v>
+        <v>3807</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Pantene Acondicionador Rizos Definidos 400ml</t>
+          <t>Suave Acondicionador Nutrición Coco 5L</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Acondicionador hidratante que desenreda al instante y da elasticidad y cuerpo a los rulos.</t>
+          <t>Acondicionador desenredante y humectante con aroma a coco en bidón institucional.</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E63" s="3" t="n"/>
+        <v>23000</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3807.jpg</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>400 ml</t>
+          <t>5 litros</t>
         </is>
       </c>
       <c r="G63" s="3" t="n"/>
@@ -2852,7 +3082,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I63" s="3" t="n"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.elpalaciodelalimpieza.com.ar</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="3" t="n"/>
     </row>
@@ -2873,7 +3107,11 @@
       <c r="D64" s="4" t="n">
         <v>6600</v>
       </c>
-      <c r="E64" s="3" t="n"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1927.jpg</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Tira x 24 sachets</t>
@@ -2910,7 +3148,11 @@
       <c r="D65" s="4" t="n">
         <v>6600</v>
       </c>
-      <c r="E65" s="3" t="n"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2746.jpg</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Tira x 24 sachets</t>
@@ -2932,25 +3174,29 @@
     </row>
     <row r="66" ht="20.1" customHeight="1">
       <c r="A66" s="2" t="n">
-        <v>10090</v>
+        <v>5014</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Franela Clásica Media Naranja</t>
+          <t>Bolsas Consorcio Negras Reforzadas 70x100</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Franela de algodón suave para lustrar, limpiar muebles, vidrios y pulir superficies sin rayar.</t>
+          <t>Bolsas negras de consorcio de alto espesor y resistencia para cargas pesadas.</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>2900</v>
-      </c>
-      <c r="E66" s="3" t="n"/>
+        <v>190</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5014.jpg</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Unidad</t>
+          <t>Unidad (venta x50)</t>
         </is>
       </c>
       <c r="G66" s="3" t="n"/>
@@ -2961,7 +3207,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/franela-clasica-media-naranja-10090</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/bolsas-70x100-negras-5014</t>
         </is>
       </c>
       <c r="J66" s="2" t="n"/>
@@ -2969,25 +3215,29 @@
     </row>
     <row r="67" ht="20.1" customHeight="1">
       <c r="A67" s="2" t="n">
-        <v>751</v>
+        <v>3521</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Fibra Verde Abrasiva 3M 12x16cm</t>
+          <t>Bolsas Consorcio Verdes 70x100cm</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Fibra abrasiva de alta calidad para fregado enérgico de fuentes, asaderas y pisos resistentes.</t>
+          <t>Bolsas de consorcio verdes para separación de residuos reciclables en edificios y empresas.</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E67" s="3" t="n"/>
+        <v>220</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3521.jpg</t>
+        </is>
+      </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>12 x 16 cm</t>
+          <t>Unidad (venta x50)</t>
         </is>
       </c>
       <c r="G67" s="3" t="n"/>
@@ -2998,7 +3248,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/fibra-verde-3m-normal-12x16cm-granel-751</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/bolsas-70x100-verdes-3521</t>
         </is>
       </c>
       <c r="J67" s="2" t="n"/>
@@ -3006,36 +3256,42 @@
     </row>
     <row r="68" ht="20.1" customHeight="1">
       <c r="A68" s="2" t="n">
-        <v>538</v>
+        <v>1099</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Mortimer Esponja Cuadriculada</t>
+          <t>Osram Dulux Mini Twist 20W</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Esponja multiuso con diseño cuadriculado de espuma sintética y fibra abrasiva integrada.</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E68" s="3" t="n"/>
+          <t>Lámpara espiral de bajo consumo, 20 W, luz blanca.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Consultar</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1099.jpg</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Unidad</t>
+          <t>20 W · Luz blanca</t>
         </is>
       </c>
       <c r="G68" s="3" t="n"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/mortimer-cuadriculada-clasica-538</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar</t>
         </is>
       </c>
       <c r="J68" s="2" t="n"/>
@@ -3043,25 +3299,29 @@
     </row>
     <row r="69" ht="20.1" customHeight="1">
       <c r="A69" s="2" t="n">
-        <v>1561</v>
+        <v>2641</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Mortimer Esponja Doble Cara</t>
+          <t>Royco Secavidrios Inoxidable 35cm</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Esponja anatómica salvaúñas con fibra abrasiva para limpieza profunda y esponja para enjabonar.</t>
+          <t>Secavidrios de acero inoxidable para limpieza de cristales.</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E69" s="3" t="n"/>
+        <v>18000</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2641.jpg</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Unidad</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="G69" s="3" t="n"/>
@@ -3072,7 +3332,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/mortimer-esp-doble-cara-1561</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/secavidrios-inoxidable-25-royco-2641</t>
         </is>
       </c>
       <c r="J69" s="2" t="n"/>
@@ -3080,25 +3340,29 @@
     </row>
     <row r="70" ht="20.1" customHeight="1">
       <c r="A70" s="2" t="n">
-        <v>5487</v>
+        <v>5062</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Make Esponja de Acero Inoxidable 50g</t>
+          <t>Secavidrios 3 en 1 con Rociador</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Espiral de acero inoxidable para fregar ollas, parrillas y suciedad pegada muy rebelde.</t>
+          <t>Limpiavidrios con rociador integrado, sistema 3 en 1.</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E70" s="3" t="n"/>
+        <v>9900</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5062.jpg</t>
+        </is>
+      </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>50 gramos</t>
+          <t>3 en 1</t>
         </is>
       </c>
       <c r="G70" s="3" t="n"/>
@@ -3109,7 +3373,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/make-esponja-inoxidable-50g-5487</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/secavidrios-3en1-rociador-5062</t>
         </is>
       </c>
       <c r="J70" s="2" t="n"/>
@@ -3117,25 +3381,29 @@
     </row>
     <row r="71" ht="20.1" customHeight="1">
       <c r="A71" s="2" t="n">
-        <v>524</v>
+        <v>3166</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Virulana Rollitos Lana de Acero x10</t>
+          <t>Royco Lavador con Abrasivo 45cm</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Rollitos de viruta fina de acero para pulido de metales, aluminio y ollas tradicionales.</t>
+          <t>Lavador de vidrios completo con abrasivo.</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2300</v>
-      </c>
-      <c r="E71" s="3" t="n"/>
+        <v>17000</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3166.jpg</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Pack x 10 un. (70g)</t>
+          <t>45 cm</t>
         </is>
       </c>
       <c r="G71" s="3" t="n"/>
@@ -3146,7 +3414,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/virulana-rollitos-x10-70g-524</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/lavador-45c-abras-completo-royco-3166</t>
         </is>
       </c>
       <c r="J71" s="2" t="n"/>
@@ -3154,25 +3422,29 @@
     </row>
     <row r="72" ht="20.1" customHeight="1">
       <c r="A72" s="2" t="n">
-        <v>55</v>
+        <v>4257</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Make Guantes de Látex Soft Mediano</t>
+          <t>Make Cabo Extensible Aluminio 2x2m</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Guantes de látex satinado para protección de las manos en tareas domésticas cotidianas.</t>
+          <t>Cabo extensible liviano de aluminio, color azul.</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1650</v>
-      </c>
-      <c r="E72" s="3" t="n"/>
+        <v>45000</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4257.jpg</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Par (Talle M)</t>
+          <t>2 tramos x 2 m</t>
         </is>
       </c>
       <c r="G72" s="3" t="n"/>
@@ -3183,7 +3455,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/make-guante-soft-mediano-55</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-extensible-aluminio-2x2-make-azul-4257</t>
         </is>
       </c>
       <c r="J72" s="2" t="n"/>
@@ -3191,25 +3463,29 @@
     </row>
     <row r="73" ht="20.1" customHeight="1">
       <c r="A73" s="2" t="n">
-        <v>733</v>
+        <v>2694</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MAPA Guantes Plissé Talle 7½-8</t>
+          <t>Cabo Extensible Profesional 3x1,50m</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Guantes profesionales de látex natural reforzado con puño plisado de máxima durabilidad.</t>
+          <t>Cabo extensible profesional de aluminio, color negro.</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E73" s="3" t="n"/>
+        <v>60000</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2694.jpg</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Par (Talle M)</t>
+          <t>3 tramos x 1,50 m</t>
         </is>
       </c>
       <c r="G73" s="3" t="n"/>
@@ -3220,7 +3496,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/mapa-guantes-plisse-7-8-med-733</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-extensible-aluminio-3x1-50m-profes-negro-2694</t>
         </is>
       </c>
       <c r="J73" s="2" t="n"/>
@@ -3228,25 +3504,29 @@
     </row>
     <row r="74" ht="20.1" customHeight="1">
       <c r="A74" s="2" t="n">
-        <v>3269</v>
+        <v>2634</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Plumita Guantes de Limpieza Mediano</t>
+          <t>Cepillo Barrendero Andén 100cm Cariño</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Guantes de látex anatómicos con palma rugosa antideslizante para agarre seguro.</t>
+          <t>Cepillo barrendero industrial de gran ancho de barrido para veredas, talleres y depósitos.</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E74" s="3" t="n"/>
+        <v>26000</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2634.jpg</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Par (Talle M)</t>
+          <t>100 cm (base madera)</t>
         </is>
       </c>
       <c r="G74" s="3" t="n"/>
@@ -3255,31 +3535,39 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I74" s="3" t="n"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.elpalaciodelalimpieza.com.ar/anden-barrendero-100-cari-o-madera-2634</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="3" t="n"/>
     </row>
     <row r="75" ht="20.1" customHeight="1">
       <c r="A75" s="2" t="n">
-        <v>1758</v>
+        <v>832</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Balde Plástico 12 Litros Romyl</t>
+          <t>Cepillo Andén de Cerda 80cm</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Balde de polipropileno reforzado con asa metálica y escala de litros para limpieza.</t>
+          <t>Cepillo para barrido fino en pisos de parquet, mosaico y cemento alisado en grandes superficies.</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E75" s="3" t="n"/>
+        <v>30000</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/832.jpg</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>12 litros</t>
+          <t>80 cm</t>
         </is>
       </c>
       <c r="G75" s="3" t="n"/>
@@ -3290,7 +3578,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/balde-12l-romyl-task-1758</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/anden-cerda-80cm-832</t>
         </is>
       </c>
       <c r="J75" s="2" t="n"/>
@@ -3298,25 +3586,29 @@
     </row>
     <row r="76" ht="20.1" customHeight="1">
       <c r="A76" s="2" t="n">
-        <v>4264</v>
+        <v>1810</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Trapo de Piso Julieta Gris 50x60cm</t>
+          <t>Secador de Piso Aluminio 100cm</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Paño de piso tejido en algodón gris de gran resistencia mecánica y alto poder secante.</t>
+          <t>Secador de aluminio para limpieza de pisos.</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E76" s="3" t="n"/>
+        <v>37500</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1810.jpg</t>
+        </is>
+      </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>50 x 60 cm</t>
+          <t>100 cm</t>
         </is>
       </c>
       <c r="G76" s="3" t="n"/>
@@ -3327,7 +3619,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/trapo-de-piso-julieta-gris-50x60cm-4264</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/secador-aluminio-100cm-piso-1810</t>
         </is>
       </c>
       <c r="J76" s="2" t="n"/>
@@ -3335,25 +3627,29 @@
     </row>
     <row r="77" ht="20.1" customHeight="1">
       <c r="A77" s="2" t="n">
-        <v>2399</v>
+        <v>100204</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Rejilla de Cocina Pesada Palacio 35x40cm</t>
+          <t>Fiorentina Secador Aqua Plus 3M</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Paño rejilla tejido pesado de algodón ideal para mesadas, bachas y utensilios de cocina.</t>
+          <t>Secador de piso Fiorentina Aqua Plus.</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E77" s="3" t="n"/>
+        <v>7000</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/100204.jpg</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>35 x 40 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="G77" s="3" t="n"/>
@@ -3364,7 +3660,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/rejilla-palacio-pesada-35x40cm-2399</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/fiorentina-secador-aqua-40cm-plus-3m-100204</t>
         </is>
       </c>
       <c r="J77" s="2" t="n"/>
@@ -3372,25 +3668,29 @@
     </row>
     <row r="78" ht="20.1" customHeight="1">
       <c r="A78" s="2" t="n">
-        <v>1451</v>
+        <v>71</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Escobillón Príncipe Max Cariño</t>
+          <t>Cabo de Madera con Rosca 1.30m</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Escobillón de cerdas plumadas para barrido suave y eficiente de polvillo en interiores.</t>
+          <t>Palo de madera de pino seleccionado con puntera a rosca universal estándar para escobas.</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E78" s="3" t="n"/>
+        <v>2000</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/71.jpg</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Sin cabo</t>
+          <t>1.30 metros</t>
         </is>
       </c>
       <c r="G78" s="3" t="n"/>
@@ -3401,7 +3701,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/escobillon-principemax-cari-o-1451</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-madera-1-30-c-rosca-71</t>
         </is>
       </c>
       <c r="J78" s="2" t="n"/>
@@ -3409,25 +3709,29 @@
     </row>
     <row r="79" ht="20.1" customHeight="1">
       <c r="A79" s="2" t="n">
-        <v>1440</v>
+        <v>1934</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Escobillón Recto Color Nº1 Romyl</t>
+          <t>Cabo de Madera Reforzado 1.50m</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Escobillón recto con cerdas sintéticas resistentes para limpieza cotidiana de pisos.</t>
+          <t>Palo largo de madera para cepillos barrenderos y secadores de piso industriales.</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E79" s="3" t="n"/>
+        <v>2500</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1934.jpg</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Sin cabo</t>
+          <t>1.50 metros</t>
         </is>
       </c>
       <c r="G79" s="3" t="n"/>
@@ -3438,7 +3742,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/escobillon-plast-recto-color-nao1-romyl-1440</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-madera-1-50m-natural-1934</t>
         </is>
       </c>
       <c r="J79" s="2" t="n"/>
@@ -3446,25 +3750,29 @@
     </row>
     <row r="80" ht="20.1" customHeight="1">
       <c r="A80" s="2" t="n">
-        <v>2634</v>
+        <v>3910</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Cepillo Barrendero Andén 100cm Cariño</t>
+          <t>Balde Centrífugo Vileda Easy Wring</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Cepillo barrendero industrial de gran ancho de barrido para veredas, talleres y depósitos.</t>
+          <t>Sistema de escurrido por pedal centrífugo para limpiar y secar pisos sin esfuerzo ni mojarse las manos.</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>26000</v>
-      </c>
-      <c r="E80" s="3" t="n"/>
+        <v>99990</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3910.jpg</t>
+        </is>
+      </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>100 cm (base madera)</t>
+          <t>Balde con pedal + mopa</t>
         </is>
       </c>
       <c r="G80" s="3" t="n"/>
@@ -3475,7 +3783,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/anden-barrendero-100-cari-o-madera-2634</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/vileda-easy-wring-balde-promo-3910</t>
         </is>
       </c>
       <c r="J80" s="2" t="n"/>
@@ -3483,25 +3791,29 @@
     </row>
     <row r="81" ht="20.1" customHeight="1">
       <c r="A81" s="2" t="n">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Cepillo Andén de Cerda 80cm</t>
+          <t>Balde Escurridor Turbo Matic Iberia Pronto</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Cepillo para barrido fino en pisos de parquet, mosaico y cemento alisado en grandes superficies.</t>
+          <t>Sistema de limpieza con mopa de microfibra y balde escurridor giratorio de alta velocidad.</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E81" s="3" t="n"/>
+        <v>95000</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/849.jpg</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>80 cm</t>
+          <t>Balde giratorio + mopa</t>
         </is>
       </c>
       <c r="G81" s="3" t="n"/>
@@ -3512,7 +3824,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/anden-cerda-80cm-832</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/iberia-pronto-turbo-matic-completo-balde-mop-849</t>
         </is>
       </c>
       <c r="J81" s="2" t="n"/>
@@ -3520,25 +3832,29 @@
     </row>
     <row r="82" ht="20.1" customHeight="1">
       <c r="A82" s="2" t="n">
-        <v>71</v>
+        <v>4195</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Cabo de Madera con Rosca 1.30m</t>
+          <t>Señal de Piso Mojado Tijera Busgran</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Palo de madera de pino seleccionado con puntera a rosca universal estándar para escobas.</t>
+          <t>Cartel de advertencia plegable amarillo con leyenda visible en ambas caras para seguridad.</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E82" s="3" t="n"/>
+        <v>21000</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4195.jpg</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>1.30 metros</t>
+          <t>Tijera plegable</t>
         </is>
       </c>
       <c r="G82" s="3" t="n"/>
@@ -3549,7 +3865,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-madera-1-30-c-rosca-71</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/se-al-piso-mojado-busgran-rubber-4195</t>
         </is>
       </c>
       <c r="J82" s="2" t="n"/>
@@ -3557,25 +3873,29 @@
     </row>
     <row r="83" ht="20.1" customHeight="1">
       <c r="A83" s="2" t="n">
-        <v>1934</v>
+        <v>5116</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Cabo de Madera Reforzado 1.50m</t>
+          <t>Cono Señalador Caution Amarillo</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Palo largo de madera para cepillos barrenderos y secadores de piso industriales.</t>
+          <t>Cono demarcatorio reflectivo de polietileno flexible para prevención y delimitación de áreas.</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E83" s="3" t="n"/>
+        <v>18000</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5116.jpg</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>1.50 metros</t>
+          <t>Mediano</t>
         </is>
       </c>
       <c r="G83" s="3" t="n"/>
@@ -3586,7 +3906,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cabo-madera-1-50m-natural-1934</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/cono-se-alador-caution-amarillo-m-disc-5116</t>
         </is>
       </c>
       <c r="J83" s="2" t="n"/>
@@ -3594,25 +3914,29 @@
     </row>
     <row r="84" ht="20.1" customHeight="1">
       <c r="A84" s="2" t="n">
-        <v>2652</v>
+        <v>1226</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Bolsas para Residuos Force 45x60cm</t>
+          <t>Extralimp Balde Mop Centrífugo</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Bolsas negras reforzadas para cestos pequeños y medianos de baño y oficina.</t>
+          <t>Balde con sistema centrífugo de acero y dos mopas.</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E84" s="3" t="n"/>
+        <v>45000</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/1226.jpg</t>
+        </is>
+      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Paq. x 30 bolsas</t>
+          <t>Balde + 2 mopas</t>
         </is>
       </c>
       <c r="G84" s="3" t="n"/>
@@ -3623,7 +3947,7 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/bolsas-45x60x30-negras-force-funda-2652</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/balde-mop-extralimp-centrifugo-acero-2-mopas-1226</t>
         </is>
       </c>
       <c r="J84" s="2" t="n"/>
@@ -3631,25 +3955,29 @@
     </row>
     <row r="85" ht="20.1" customHeight="1">
       <c r="A85" s="2" t="n">
-        <v>3521</v>
+        <v>122</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Bolsas Consorcio Verdes 70x100cm</t>
+          <t>Iberia WindoMatic Limpiavidrios</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Bolsas de consorcio verdes para separación de residuos reciclables en edificios y empresas.</t>
+          <t>Sistema todo en uno con spray, mopa, escobilla y cabo extensible.</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="E85" s="3" t="n"/>
+        <v>52000</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/122.jpg</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Unidad (venta x50)</t>
+          <t>Todo en uno</t>
         </is>
       </c>
       <c r="G85" s="3" t="n"/>
@@ -3660,7 +3988,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/bolsas-70x100-verdes-3521</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar</t>
         </is>
       </c>
       <c r="J85" s="2" t="n"/>
@@ -3668,25 +3996,29 @@
     </row>
     <row r="86" ht="20.1" customHeight="1">
       <c r="A86" s="2" t="n">
-        <v>5014</v>
+        <v>6732</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Bolsas Consorcio Negras Reforzadas 70x100</t>
+          <t>Kendy Cesto Ecológico Gris 60L</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Bolsas negras de consorcio de alto espesor y resistencia para cargas pesadas.</t>
+          <t>Recipiente para basura con tapa vaivén, color gris.</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="E86" s="3" t="n"/>
+        <v>80000</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/6732.jpg</t>
+        </is>
+      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Unidad (venta x50)</t>
+          <t>60 litros</t>
         </is>
       </c>
       <c r="G86" s="3" t="n"/>
@@ -3697,7 +4029,7 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/bolsas-70x100-negras-5014</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/recipiente-60l-ecologico-t-vaiven-kendy-promo-6732</t>
         </is>
       </c>
       <c r="J86" s="2" t="n"/>
@@ -3705,25 +4037,29 @@
     </row>
     <row r="87" ht="20.1" customHeight="1">
       <c r="A87" s="2" t="n">
-        <v>100219</v>
+        <v>6733</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Cesto de Residuos 65L con Tapa Busgran</t>
+          <t>Kendy Cesto Reciclable Verde 60L</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Contenedor plástico para residuos pesados de 65 litros con tapa rebatible.</t>
+          <t>Recipiente para reciclables con tapa vaivén, color verde.</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E87" s="3" t="n"/>
+        <v>80000</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/6733.jpg</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>65 litros</t>
+          <t>60 litros</t>
         </is>
       </c>
       <c r="G87" s="3" t="n"/>
@@ -3734,7 +4070,7 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/recipiente-residuos-65l-c-tapa-busgrandph-pesado-100219</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/recipiente-60l-ecologico-t-vaiven-kendy-verde-recicla-6733</t>
         </is>
       </c>
       <c r="J87" s="2" t="n"/>
@@ -3742,25 +4078,29 @@
     </row>
     <row r="88" ht="20.1" customHeight="1">
       <c r="A88" s="2" t="n">
-        <v>4195</v>
+        <v>3778</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Señal de Piso Mojado Tijera Busgran</t>
+          <t>Contenedor con Ruedas Azul 120L</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Cartel de advertencia plegable amarillo con leyenda visible en ambas caras para seguridad.</t>
+          <t>Contenedor de residuos con ruedas, color azul.</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E88" s="3" t="n"/>
+        <v>200000</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3778.jpg</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Tijera plegable</t>
+          <t>120 litros</t>
         </is>
       </c>
       <c r="G88" s="3" t="n"/>
@@ -3771,7 +4111,7 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/se-al-piso-mojado-busgran-rubber-4195</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/contenedor-industrial-c-ruedas-120l-azul-3778</t>
         </is>
       </c>
       <c r="J88" s="2" t="n"/>
@@ -3779,25 +4119,29 @@
     </row>
     <row r="89" ht="20.1" customHeight="1">
       <c r="A89" s="2" t="n">
-        <v>5116</v>
+        <v>3783</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Cono Señalador Caution Amarillo</t>
+          <t>Contenedor con Ruedas Negro 120L</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Cono demarcatorio reflectivo de polietileno flexible para prevención y delimitación de áreas.</t>
+          <t>Contenedor de residuos con ruedas, color negro.</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E89" s="3" t="n"/>
+        <v>200000</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3783.jpg</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Mediano</t>
+          <t>120 litros</t>
         </is>
       </c>
       <c r="G89" s="3" t="n"/>
@@ -3808,7 +4152,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/cono-se-alador-caution-amarillo-m-disc-5116</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/contenedor-industrial-c-ruedas-120l-negro-3783</t>
         </is>
       </c>
       <c r="J89" s="2" t="n"/>
@@ -3816,25 +4160,29 @@
     </row>
     <row r="90" ht="20.1" customHeight="1">
       <c r="A90" s="2" t="n">
-        <v>3910</v>
+        <v>3776</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Balde Centrífugo Vileda Easy Wring</t>
+          <t>Contenedor con Ruedas Rojo 120L</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Sistema de escurrido por pedal centrífugo para limpiar y secar pisos sin esfuerzo ni mojarse las manos.</t>
+          <t>Contenedor de residuos con ruedas, color rojo.</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>99990</v>
-      </c>
-      <c r="E90" s="3" t="n"/>
+        <v>200000</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3776.jpg</t>
+        </is>
+      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Balde con pedal + mopa</t>
+          <t>120 litros</t>
         </is>
       </c>
       <c r="G90" s="3" t="n"/>
@@ -3845,7 +4193,7 @@
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/vileda-easy-wring-balde-promo-3910</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/contenedor-industrial-c-ruedas-120l-rojo-3776</t>
         </is>
       </c>
       <c r="J90" s="2" t="n"/>
@@ -3853,25 +4201,29 @@
     </row>
     <row r="91" ht="20.1" customHeight="1">
       <c r="A91" s="2" t="n">
-        <v>849</v>
+        <v>3998</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Balde Escurridor Turbo Matic Iberia Pronto</t>
+          <t>Contenedor con Ruedas Verde 120L</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Sistema de limpieza con mopa de microfibra y balde escurridor giratorio de alta velocidad.</t>
+          <t>Contenedor de residuos con ruedas, color verde.</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E91" s="3" t="n"/>
+        <v>200000</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3998.jpg</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Balde giratorio + mopa</t>
+          <t>120 litros</t>
         </is>
       </c>
       <c r="G91" s="3" t="n"/>
@@ -3882,7 +4234,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/iberia-pronto-turbo-matic-completo-balde-mop-849</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/contenedor-industrial-120l-3998</t>
         </is>
       </c>
       <c r="J91" s="2" t="n"/>
@@ -3890,25 +4242,29 @@
     </row>
     <row r="92" ht="20.1" customHeight="1">
       <c r="A92" s="2" t="n">
-        <v>4329</v>
+        <v>2167</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Carro Portaelementos de Limpieza Make</t>
+          <t>Dispenser Jabón Líquido a Tecla Palacio</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Carro móvil para transporte ordenado de baldes, químicos y paños de maestranza.</t>
+          <t>Dosificador de pared con botón tecla y ventana visor para control de carga de jabón líquido.</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E92" s="3" t="n"/>
+        <v>14000</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2167.jpg</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Estructura rodante</t>
+          <t>Plástico ABS</t>
         </is>
       </c>
       <c r="G92" s="3" t="n"/>
@@ -3919,7 +4275,7 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/carro-portaelementos-make-4329</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-jabon-liq-plast-palacio-2167</t>
         </is>
       </c>
       <c r="J92" s="2" t="n"/>
@@ -3927,25 +4283,29 @@
     </row>
     <row r="93" ht="20.1" customHeight="1">
       <c r="A93" s="2" t="n">
-        <v>3811</v>
+        <v>2595</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Carro de Lavandería con Bolsa Make</t>
+          <t>Dispenser Jabón Líquido Acero Inoxidable</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Carro institucional para traslado higiénico de ropa blanca, toallas y sábanas.</t>
+          <t>Dosificador institucional antivandálico de acero inoxidable con cerradura de seguridad.</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>280000</v>
-      </c>
-      <c r="E93" s="3" t="n"/>
+        <v>75000</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2595.jpg</t>
+        </is>
+      </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Carro con bolsa vinílica</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="G93" s="3" t="n"/>
@@ -3956,7 +4316,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/carro-lavanderia-c-bolsa-make-3811</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-jabon-liquido-inoxidable-2595</t>
         </is>
       </c>
       <c r="J93" s="2" t="n"/>
@@ -3964,25 +4324,29 @@
     </row>
     <row r="94" ht="20.1" customHeight="1">
       <c r="A94" s="2" t="n">
-        <v>3619</v>
+        <v>5340</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Carro Multifunción Institucional Make</t>
+          <t>Dispenser Toalla Intercalada Blanco PP</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Carro integral de limpieza para reposición y servicio en hoteles, sanatorios y colegios.</t>
+          <t>Dispensador de pared compacto para toallas de papel intercaladas con traba de seguridad.</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>280000</v>
-      </c>
-      <c r="E94" s="3" t="n"/>
+        <v>16000</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5340.jpg</t>
+        </is>
+      </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Carro con estantes y bolsa</t>
+          <t>Capacidad 1 carga</t>
         </is>
       </c>
       <c r="G94" s="3" t="n"/>
@@ -3993,7 +4357,7 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/carro-multifuncion-make-3619</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-toalla-interc-visor-blanco-1carga-5340</t>
         </is>
       </c>
       <c r="J94" s="2" t="n"/>
@@ -4001,25 +4365,29 @@
     </row>
     <row r="95" ht="20.1" customHeight="1">
       <c r="A95" s="2" t="n">
-        <v>5803</v>
+        <v>100104</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Carro Doble Balde 20L con Prensa Royco</t>
+          <t>Dispenser Toalla Intercalada Acero Inox</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Carro profesional para fregado con separación de agua limpia y sucia y prensa escurridora reforzada.</t>
+          <t>Gabinete dispensador de acero inoxidable esmerilado para toallas intercaladas en baños de alto nivel.</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>130000</v>
-      </c>
-      <c r="E95" s="3" t="n"/>
+        <v>78000</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/100104.jpg</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2 baldes x 20L + prensa</t>
+          <t>Acero inoxidable</t>
         </is>
       </c>
       <c r="G95" s="3" t="n"/>
@@ -4030,7 +4398,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/carro-20l-doble-c-prensa-royco-5803</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-toalla-interc-inoxidable-100104</t>
         </is>
       </c>
       <c r="J95" s="2" t="n"/>
@@ -4038,25 +4406,29 @@
     </row>
     <row r="96" ht="20.1" customHeight="1">
       <c r="A96" s="2" t="n">
-        <v>7250</v>
+        <v>3675</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Tótem Dispenser Alcohol en Gel Manos Libres</t>
+          <t>Evolution Dispenser Higiénico Jumbo</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Dispositivo mecánico de pie accionado por pedal para sanitización segura sin contacto manual.</t>
+          <t>Dispenser blanco de polipropileno para papel higiénico jumbo de 600 m.</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E96" s="3" t="n"/>
+        <v>20000</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3675.jpg</t>
+        </is>
+      </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Tótem a pedal</t>
+          <t>Rollo hasta 600 m</t>
         </is>
       </c>
       <c r="G96" s="3" t="n"/>
@@ -4067,7 +4439,7 @@
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-alcohol-gel-manos-libres-totem-palacio-mas-7250</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-higienico-jumbo-600m-evolution-blanco-polipropilen-3675</t>
         </is>
       </c>
       <c r="J96" s="2" t="n"/>
@@ -4075,25 +4447,29 @@
     </row>
     <row r="97" ht="20.1" customHeight="1">
       <c r="A97" s="2" t="n">
-        <v>100327</v>
+        <v>2687</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Toalla en Rollo a Palanca ABS</t>
+          <t>Dispenser Papel Higiénico Jumbo Acero Inox</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Dispensador institucional cerrado con accionamiento a palanca para toallas de papel en rollo.</t>
+          <t>Portarrollo gigante de máxima capacidad en acero inoxidable para sanitarios de alto tránsito.</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>135000</v>
-      </c>
-      <c r="E97" s="3" t="n"/>
+        <v>105000</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/2687.jpg</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Bobina hasta 300m</t>
+          <t>Bobina hasta 600m</t>
         </is>
       </c>
       <c r="G97" s="3" t="n"/>
@@ -4104,7 +4480,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-toalla-rollo-palanca-300m-100327</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/disp-acero-inox-higienico-600m-2687</t>
         </is>
       </c>
       <c r="J97" s="2" t="n"/>
@@ -4112,25 +4488,29 @@
     </row>
     <row r="98" ht="20.1" customHeight="1">
       <c r="A98" s="2" t="n">
-        <v>2167</v>
+        <v>4329</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Jabón Líquido a Tecla Palacio</t>
+          <t>Carro Portaelementos de Limpieza Make</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Dosificador de pared con botón tecla y ventana visor para control de carga de jabón líquido.</t>
+          <t>Carro móvil para transporte ordenado de baldes, químicos y paños de maestranza.</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E98" s="3" t="n"/>
+        <v>250000</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/4329.jpg</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Plástico ABS</t>
+          <t>Estructura rodante</t>
         </is>
       </c>
       <c r="G98" s="3" t="n"/>
@@ -4141,7 +4521,7 @@
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-jabon-liq-plast-palacio-2167</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/carro-portaelementos-make-4329</t>
         </is>
       </c>
       <c r="J98" s="2" t="n"/>
@@ -4149,25 +4529,29 @@
     </row>
     <row r="99" ht="20.1" customHeight="1">
       <c r="A99" s="2" t="n">
-        <v>2595</v>
+        <v>3811</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Jabón Líquido Acero Inoxidable</t>
+          <t>Carro de Lavandería con Bolsa Make</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Dosificador institucional antivandálico de acero inoxidable con cerradura de seguridad.</t>
+          <t>Carro institucional para traslado higiénico de ropa blanca, toallas y sábanas.</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E99" s="3" t="n"/>
+        <v>280000</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3811.jpg</t>
+        </is>
+      </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>Carro con bolsa vinílica</t>
         </is>
       </c>
       <c r="G99" s="3" t="n"/>
@@ -4178,7 +4562,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-jabon-liquido-inoxidable-2595</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/carro-lavanderia-c-bolsa-make-3811</t>
         </is>
       </c>
       <c r="J99" s="2" t="n"/>
@@ -4186,25 +4570,29 @@
     </row>
     <row r="100" ht="20.1" customHeight="1">
       <c r="A100" s="2" t="n">
-        <v>5340</v>
+        <v>3619</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Toalla Intercalada Blanco PP</t>
+          <t>Carro Multifunción Institucional Make</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Dispensador de pared compacto para toallas de papel intercaladas con traba de seguridad.</t>
+          <t>Carro integral de limpieza para reposición y servicio en hoteles, sanatorios y colegios.</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E100" s="3" t="n"/>
+        <v>280000</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/3619.jpg</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Capacidad 1 carga</t>
+          <t>Carro con estantes y bolsa</t>
         </is>
       </c>
       <c r="G100" s="3" t="n"/>
@@ -4215,7 +4603,7 @@
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-toalla-interc-visor-blanco-1carga-5340</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/carro-multifuncion-make-3619</t>
         </is>
       </c>
       <c r="J100" s="2" t="n"/>
@@ -4223,25 +4611,29 @@
     </row>
     <row r="101" ht="20.1" customHeight="1">
       <c r="A101" s="2" t="n">
-        <v>100104</v>
+        <v>5803</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Toalla Intercalada Acero Inox</t>
+          <t>Carro Doble Balde 20L con Prensa Royco</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Gabinete dispensador de acero inoxidable esmerilado para toallas intercaladas en baños de alto nivel.</t>
+          <t>Carro profesional para fregado con separación de agua limpia y sucia y prensa escurridora reforzada.</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>78000</v>
-      </c>
-      <c r="E101" s="3" t="n"/>
+        <v>130000</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/5803.jpg</t>
+        </is>
+      </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Acero inoxidable</t>
+          <t>2 baldes x 20L + prensa</t>
         </is>
       </c>
       <c r="G101" s="3" t="n"/>
@@ -4252,7 +4644,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-toalla-interc-inoxidable-100104</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/carro-20l-doble-c-prensa-royco-5803</t>
         </is>
       </c>
       <c r="J101" s="2" t="n"/>
@@ -4260,25 +4652,29 @@
     </row>
     <row r="102" ht="20.1" customHeight="1">
       <c r="A102" s="2" t="n">
-        <v>2166</v>
+        <v>100191</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Papel Higiénico Jumbo ABS</t>
+          <t>Felpudo Print Welcome 30x70cm</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Portarrollo institucional de pared en plástico ABS para rollos de papel higiénico gigante.</t>
+          <t>Felpudo con diseño Welcome para entradas.</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E102" s="3" t="n"/>
+        <v>18000</v>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/100191.jpg</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Rollo 300 / 350m</t>
+          <t>30 x 70 cm</t>
         </is>
       </c>
       <c r="G102" s="3" t="n"/>
@@ -4289,33 +4685,40 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/dispenser-higienico-jumbo-300-350m-2166</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/felpudo-captor-print-welcome-30x70cm-vl-fg-100191</t>
         </is>
       </c>
       <c r="J102" s="2" t="n"/>
       <c r="K102" s="3" t="n"/>
     </row>
     <row r="103" ht="20.1" customHeight="1">
-      <c r="A103" s="2" t="n">
-        <v>2687</v>
-      </c>
+      <c r="A103" s="2" t="n"/>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Dispenser Papel Higiénico Jumbo Acero Inox</t>
+          <t>Felpudos personalizados</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Portarrollo gigante de máxima capacidad en acero inoxidable para sanitarios de alto tránsito.</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="n">
-        <v>105000</v>
-      </c>
-      <c r="E103" s="3" t="n"/>
+          <t>Fabricamos tu felpudo a pedido con el logo que nos pases.
+La cotización depende de las medidas y de si lo querés con borde o sin borde.
+El logo debe enviarse obligatoriamente en formato vectorizado: Corel (.cdr) o SVG (.svg).
+Al confirmar el pedido, se abona el 50% del valor como seña para comenzar la fabricación.</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>A cotizar</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>imagenes/personalizado.jpg</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Bobina hasta 600m</t>
+          <t>A medida</t>
         </is>
       </c>
       <c r="G103" s="3" t="n"/>
@@ -4326,14 +4729,123 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar/disp-acero-inox-higienico-600m-2687</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar</t>
         </is>
       </c>
       <c r="J103" s="2" t="n"/>
       <c r="K103" s="3" t="n"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:L103"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/catalogo_productos.xlsx
+++ b/catalogo_productos.xlsx
@@ -3256,42 +3256,40 @@
     </row>
     <row r="68" ht="20.1" customHeight="1">
       <c r="A68" s="2" t="n">
-        <v>1099</v>
+        <v>10999</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Osram Dulux Mini Twist 20W</t>
+          <t>Royco Secavidrios Aluminio 35cm</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Lámpara espiral de bajo consumo, 20 W, luz blanca.</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Consultar</t>
-        </is>
+          <t>Secavidrios de aluminio, color gris, para limpieza de cristales.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>9500</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>imagenes/1099.jpg</t>
+          <t>imagenes/10999.jpg</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>20 W · Luz blanca</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="G68" s="3" t="n"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>https://www.elpalaciodelalimpieza.com.ar</t>
+          <t>https://www.elpalaciodelalimpieza.com.ar/secavidrios-aluminio-35-gris-royco-10999</t>
         </is>
       </c>
       <c r="J68" s="2" t="n"/>
